--- a/data/xlsx/bjma--compliance-and-sustainability-issues.xlsx
+++ b/data/xlsx/bjma--compliance-and-sustainability-issues.xlsx
@@ -692,7 +692,9 @@
       <c r="C16" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="31" t="n">
         <v>5</v>
       </c>
@@ -714,7 +716,9 @@
       <c r="C17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="31" t="n"/>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="31" t="n">
         <v>5</v>
       </c>
@@ -736,7 +740,9 @@
       <c r="C18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="31" t="n">
         <v>5</v>
       </c>
@@ -758,7 +764,9 @@
       <c r="C19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n"/>
+      <c r="D19" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="31" t="n">
         <v>5</v>
       </c>
@@ -780,7 +788,9 @@
       <c r="C20" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="31" t="n"/>
+      <c r="D20" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="31" t="n">
         <v>5</v>
       </c>
@@ -802,7 +812,9 @@
       <c r="C21" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="31" t="n">
         <v>4</v>
       </c>
@@ -824,7 +836,9 @@
       <c r="C22" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="31" t="n"/>
+      <c r="D22" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="31" t="n">
         <v>6</v>
       </c>
@@ -846,7 +860,9 @@
       <c r="C23" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="31" t="n"/>
+      <c r="D23" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="31" t="n">
         <v>6</v>
       </c>
@@ -868,7 +884,9 @@
       <c r="C24" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="31" t="n"/>
+      <c r="D24" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="31" t="n">
         <v>5</v>
       </c>
@@ -890,7 +908,9 @@
       <c r="C25" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="31" t="n"/>
+      <c r="D25" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="31" t="n">
         <v>5</v>
       </c>
@@ -912,7 +932,9 @@
       <c r="C26" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="31" t="n">
         <v>3</v>
       </c>
@@ -934,7 +956,9 @@
       <c r="C27" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="31" t="n"/>
+      <c r="D27" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="31" t="n">
         <v>6</v>
       </c>
@@ -956,7 +980,9 @@
       <c r="C28" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="31" t="n">
         <v>6</v>
       </c>
